--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N80_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N80_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.92607773817835</v>
+        <v>3.237987632453982</v>
       </c>
       <c r="D2" t="n">
-        <v>19.58678586708497</v>
+        <v>3.182852703401308</v>
       </c>
       <c r="E2" t="n">
-        <v>1.99632567219032</v>
+        <v>0.324402921730927</v>
       </c>
       <c r="F2" t="n">
-        <v>2.051249563968527</v>
+        <v>0.3333280541448856</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.93169185135288</v>
+        <v>2.751399925844843</v>
       </c>
       <c r="D3" t="n">
-        <v>16.14703871697869</v>
+        <v>2.623893791509038</v>
       </c>
       <c r="E3" t="n">
-        <v>1.99632567219032</v>
+        <v>0.324402921730927</v>
       </c>
       <c r="F3" t="n">
-        <v>2.051249563968527</v>
+        <v>0.3333280541448856</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.72567624021868</v>
+        <v>2.717922389035536</v>
       </c>
       <c r="D4" t="n">
-        <v>16.93348107188068</v>
+        <v>2.751690674180611</v>
       </c>
       <c r="E4" t="n">
-        <v>1.99632567219032</v>
+        <v>0.324402921730927</v>
       </c>
       <c r="F4" t="n">
-        <v>2.051249563968527</v>
+        <v>0.3333280541448856</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.42469461254819</v>
+        <v>3.481512874539082</v>
       </c>
       <c r="D5" t="n">
-        <v>21.2676784475396</v>
+        <v>3.455997747725185</v>
       </c>
       <c r="E5" t="n">
-        <v>1.99632567219032</v>
+        <v>0.324402921730927</v>
       </c>
       <c r="F5" t="n">
-        <v>2.051249563968527</v>
+        <v>0.3333280541448856</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
